--- a/skills一覧.xlsx
+++ b/skills一覧.xlsx
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>別PCで続きをやるための引き継ぎメモを、リポジトリ直下の `質疑応答M-D.MD` に作成・追記。結論・決定・未解決TODOを残す。Cursor チャット履歴は端末に残る前提。</t>
+          <t>別チャット・別担当・別マシン向けに、最新状態の引継ぎ書.mdを1ファイルで更新する</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>「別PC用に残して」「引き継ぎ書いて」「質疑応答に落として」「続きは別端末で」と明示されたとき。通常の備忘録は `/session-recap`</t>
+          <t>「引き継いで」「引継ぎ書を作って／更新して」と明示されたとき。通常の備忘録は /session-recap</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>今の会話を `備忘録.md` の日付エントリにする（決定・調査・次のTODO）。コード変更履歴用の `変更履歴.md` には書かない。</t>
+          <t>今の会話を備忘録.mdの日付エントリにする（決定・調査・次のTODO）。コード変更履歴用の変更履歴.mdには書かない</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>「まとめて」「備忘録に残して」「このやり取りを記録して」と明示されたときだけ</t>
+          <t>「まとめて」「備忘録に残して」「このやり取りを記録して」と明示されたとき。引継ぎは /chat-handoff</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>別PCで続きをやるための引き継ぎメモを、リポジトリ直下の `質疑応答M-D.MD` に作成・追記。結論・決定・未解決TODOを残す。Cursor チャット履歴は端末に残る前提。</t>
+          <t>別チャット・別担当・別マシン向けに、最新状態の引継ぎ書.mdを1ファイルで更新する</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>「別PC用に残して」「引き継ぎ書いて」「質疑応答に落として」「続きは別端末で」と明示されたとき。通常の備忘録は `/session-recap`</t>
+          <t>「引き継いで」「引継ぎ書を作って／更新して」と明示されたとき。通常の備忘録は /session-recap</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>今の会話を `備忘録.md` の日付エントリにする（決定・調査・次のTODO）。コード変更履歴用の `変更履歴.md` には書かない。</t>
+          <t>今の会話を備忘録.mdの日付エントリにする（決定・調査・次のTODO）。コード変更履歴用の変更履歴.mdには書かない</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>「まとめて」「備忘録に残して」「このやり取りを記録して」と明示されたときだけ</t>
+          <t>「まとめて」「備忘録に残して」「このやり取りを記録して」と明示されたとき。引継ぎは /chat-handoff</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
